--- a/data/Glossario_SINISA.xlsx
+++ b/data/Glossario_SINISA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5693c7b9f8509ed3/Streamlit/SINISA/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5693c7b9f8509ed3/Streamlit/SINISA/github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{8027E036-0F3C-4B05-BA0A-69D1F0DF0F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{975AB1A6-757C-4CE5-AF9A-109CE7767A9E}"/>
@@ -6699,279 +6699,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
@@ -7036,223 +6763,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7413,6 +6923,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFF9E7"/>
         </patternFill>
       </fill>
@@ -7421,6 +6938,419 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7476,6 +7406,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
@@ -7498,6 +7442,27 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7532,6 +7497,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
@@ -7540,6 +7512,34 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7623,6 +7623,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFF9E7"/>
         </patternFill>
       </fill>
@@ -7644,13 +7651,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
@@ -7658,7 +7658,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+          <bgColor rgb="FFFFF9E7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7707,14 +7707,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+          <bgColor rgb="FFFFF9E7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF9E7"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -29725,11 +29725,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L396:O396">
-    <cfRule type="expression" dxfId="147" priority="163">
+    <cfRule type="expression" dxfId="147" priority="164">
+      <formula>$G396="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="163">
       <formula>$G396="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="164">
-      <formula>$G396="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L399:O400">
@@ -29757,25 +29757,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61">
-    <cfRule type="expression" dxfId="139" priority="76">
-      <formula>$G61="Campo Automático"</formula>
+    <cfRule type="expression" dxfId="139" priority="75">
+      <formula>$G61="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="78">
+    <cfRule type="expression" dxfId="138" priority="76">
       <formula>$G61="Campo Automático"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="137" priority="77">
       <formula>$G61="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="75">
-      <formula>$G61="NÃO"</formula>
+    <cfRule type="expression" dxfId="136" priority="78">
+      <formula>$G61="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P78:P80">
-    <cfRule type="expression" dxfId="135" priority="156">
+    <cfRule type="expression" dxfId="135" priority="155">
+      <formula>$G78="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="134" priority="156">
       <formula>$G78="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="134" priority="155">
-      <formula>$G78="NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P79">
@@ -29811,59 +29811,59 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P88">
-    <cfRule type="expression" dxfId="125" priority="73">
+    <cfRule type="expression" dxfId="125" priority="79">
       <formula>$G88="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="79">
+    <cfRule type="expression" dxfId="124" priority="81">
       <formula>$G88="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="80">
+    <cfRule type="expression" dxfId="123" priority="82">
       <formula>$G88="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="81">
+    <cfRule type="expression" dxfId="122" priority="70">
+      <formula>$G88="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="121" priority="69">
       <formula>$G88="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="82">
+    <cfRule type="expression" dxfId="120" priority="71">
+      <formula>$G88="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="119" priority="72">
       <formula>$G88="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="72">
-      <formula>$G88="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="119" priority="43">
+    <cfRule type="expression" dxfId="118" priority="73">
       <formula>$G88="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="70">
+    <cfRule type="expression" dxfId="117" priority="74">
       <formula>$G88="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="69">
-      <formula>$G88="NÃO"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="116" priority="39">
       <formula>$G88="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="115" priority="41">
+    <cfRule type="expression" dxfId="115" priority="44">
+      <formula>$G88="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="114" priority="43">
       <formula>$G88="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="114" priority="42">
-      <formula>$G88="Campo Automático"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="113" priority="152">
       <formula>$G88="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="44">
+    <cfRule type="expression" dxfId="112" priority="151">
+      <formula>$G88="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="40">
       <formula>$G88="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="111" priority="74">
+    <cfRule type="expression" dxfId="110" priority="42">
       <formula>$G88="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="71">
+    <cfRule type="expression" dxfId="109" priority="80">
+      <formula>$G88="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="41">
       <formula>$G88="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="151">
-      <formula>$G88="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="108" priority="40">
-      <formula>$G88="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P90:P92 P100">
@@ -29891,11 +29891,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P101">
-    <cfRule type="expression" dxfId="101" priority="141">
+    <cfRule type="expression" dxfId="101" priority="142">
+      <formula>#REF!="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="141">
       <formula>#REF!="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="142">
-      <formula>#REF!="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P114">
@@ -29923,110 +29923,110 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P122:P123">
-    <cfRule type="expression" dxfId="93" priority="114">
+    <cfRule type="expression" dxfId="93" priority="113">
+      <formula>$G122="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="114">
       <formula>$G122="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="113">
-      <formula>$G122="NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P125:P127">
-    <cfRule type="expression" dxfId="91" priority="112">
+    <cfRule type="expression" dxfId="91" priority="111">
+      <formula>$G125="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="112">
       <formula>$G125="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="111">
-      <formula>$G125="NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P129">
-    <cfRule type="expression" dxfId="89" priority="32">
+    <cfRule type="expression" dxfId="89" priority="53">
+      <formula>$G129="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="46">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="37">
+    <cfRule type="expression" dxfId="87" priority="54">
+      <formula>$G129="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="55">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="51">
+    <cfRule type="expression" dxfId="85" priority="56">
+      <formula>$G129="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="21">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="56">
+    <cfRule type="expression" dxfId="83" priority="22">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="55">
+    <cfRule type="expression" dxfId="82" priority="23">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="54">
+    <cfRule type="expression" dxfId="81" priority="24">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="53">
+    <cfRule type="expression" dxfId="80" priority="25">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="52">
+    <cfRule type="expression" dxfId="79" priority="26">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="50">
+    <cfRule type="expression" dxfId="78" priority="27">
+      <formula>$G129="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="28">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="49">
+    <cfRule type="expression" dxfId="76" priority="29">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="24">
+    <cfRule type="expression" dxfId="75" priority="30">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="48">
+    <cfRule type="expression" dxfId="74" priority="31">
+      <formula>$G129="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="32">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="47">
+    <cfRule type="expression" dxfId="72" priority="33">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="46">
+    <cfRule type="expression" dxfId="71" priority="34">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="45">
+    <cfRule type="expression" dxfId="70" priority="48">
+      <formula>$G129="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="35">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="22">
+    <cfRule type="expression" dxfId="68" priority="38">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="38">
+    <cfRule type="expression" dxfId="67" priority="36">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="21">
+    <cfRule type="expression" dxfId="66" priority="47">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="23">
+    <cfRule type="expression" dxfId="65" priority="49">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="25">
+    <cfRule type="expression" dxfId="64" priority="45">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="26">
+    <cfRule type="expression" dxfId="63" priority="37">
+      <formula>$G129="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="50">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="27">
+    <cfRule type="expression" dxfId="61" priority="51">
       <formula>$G129="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="28">
-      <formula>$G129="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="29">
-      <formula>$G129="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="30">
-      <formula>$G129="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="31">
-      <formula>$G129="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="33">
-      <formula>$G129="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="34">
-      <formula>$G129="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="35">
-      <formula>$G129="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="36">
+    <cfRule type="expression" dxfId="60" priority="52">
       <formula>$G129="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30039,101 +30039,101 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P135">
-    <cfRule type="expression" dxfId="57" priority="4">
+    <cfRule type="expression" dxfId="57" priority="19">
+      <formula>$G135="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="20">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="5">
+    <cfRule type="expression" dxfId="55" priority="57">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6">
+    <cfRule type="expression" dxfId="54" priority="58">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="7">
+    <cfRule type="expression" dxfId="53" priority="60">
+      <formula>$G135="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="61">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="8">
+    <cfRule type="expression" dxfId="51" priority="62">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="9">
+    <cfRule type="expression" dxfId="50" priority="63">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="10">
+    <cfRule type="expression" dxfId="49" priority="64">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="11">
+    <cfRule type="expression" dxfId="48" priority="65">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="12">
+    <cfRule type="expression" dxfId="47" priority="66">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="14">
+    <cfRule type="expression" dxfId="46" priority="67">
+      <formula>$G135="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="68">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="15">
+    <cfRule type="expression" dxfId="44" priority="59">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="16">
+    <cfRule type="expression" dxfId="43" priority="3">
+      <formula>$G135="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="4">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="3">
+    <cfRule type="expression" dxfId="41" priority="5">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="18">
+    <cfRule type="expression" dxfId="40" priority="6">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="19">
+    <cfRule type="expression" dxfId="39" priority="7">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="13">
+    <cfRule type="expression" dxfId="38" priority="8">
+      <formula>$G135="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="9">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="20">
+    <cfRule type="expression" dxfId="36" priority="10">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="62">
+    <cfRule type="expression" dxfId="35" priority="11">
+      <formula>$G135="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="12">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="60">
+    <cfRule type="expression" dxfId="33" priority="13">
+      <formula>$G135="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="14">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="59">
+    <cfRule type="expression" dxfId="31" priority="15">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="58">
+    <cfRule type="expression" dxfId="30" priority="16">
       <formula>$G135="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="57">
+    <cfRule type="expression" dxfId="29" priority="105">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="64">
+    <cfRule type="expression" dxfId="28" priority="106">
       <formula>$G135="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="66">
-      <formula>$G135="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="67">
-      <formula>$G135="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="68">
-      <formula>$G135="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="105">
-      <formula>$G135="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="65">
-      <formula>$G135="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="106">
-      <formula>$G135="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="63">
-      <formula>$G135="NÃO"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="27" priority="17">
       <formula>$G135="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="61">
-      <formula>$G135="NÃO"</formula>
+    <cfRule type="expression" dxfId="26" priority="18">
+      <formula>$G135="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P137:P139">
@@ -30145,27 +30145,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P141:P142">
-    <cfRule type="expression" dxfId="23" priority="129">
+    <cfRule type="expression" dxfId="23" priority="130">
+      <formula>#REF!="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="129">
       <formula>#REF!="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="130">
-      <formula>#REF!="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P144:P145">
-    <cfRule type="expression" dxfId="21" priority="125">
+    <cfRule type="expression" dxfId="21" priority="126">
+      <formula>#REF!="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="125">
       <formula>#REF!="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="126">
-      <formula>#REF!="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P147:P150">
-    <cfRule type="expression" dxfId="19" priority="101">
+    <cfRule type="expression" dxfId="19" priority="102">
+      <formula>#REF!="Campo Automático"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="101">
       <formula>#REF!="NÃO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="102">
-      <formula>#REF!="Campo Automático"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P164:P175">
@@ -30177,11 +30177,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P182">
-    <cfRule type="expression" dxfId="15" priority="174">
+    <cfRule type="expression" dxfId="15" priority="173">
+      <formula>#REF!="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="174">
       <formula>#REF!="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="173">
-      <formula>#REF!="NÃO"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="175">
       <formula>#REF!="NÃO"</formula>
@@ -30197,31 +30197,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P185">
-    <cfRule type="expression" dxfId="9" priority="172">
+    <cfRule type="expression" dxfId="9" priority="168">
       <formula>#REF!="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="170">
+    <cfRule type="expression" dxfId="8" priority="169">
+      <formula>#REF!="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="170">
       <formula>#REF!="Campo Automático"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="171">
+    <cfRule type="expression" dxfId="6" priority="171">
       <formula>#REF!="NÃO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="168">
+    <cfRule type="expression" dxfId="5" priority="172">
       <formula>#REF!="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="169">
-      <formula>#REF!="NÃO"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="167">
       <formula>#REF!="NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P197">
-    <cfRule type="expression" dxfId="3" priority="98">
+    <cfRule type="expression" dxfId="3" priority="97">
+      <formula>$G197="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="98">
       <formula>$G197="Campo Automático"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="97">
-      <formula>$G197="NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P395">
@@ -30241,26 +30241,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="21441324-80bd-4496-af88-aea3a97193ac">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c886050a-9ad4-40b4-a6a1-233234e508b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100214BDEEF99D212469DD5CBAE3676930B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="ab08ec8871955bb65e88bcb658a2711a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="21441324-80bd-4496-af88-aea3a97193ac" xmlns:ns3="c886050a-9ad4-40b4-a6a1-233234e508b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bf1ae4c5eb403d1529f7fdc9759ee18" ns2:_="" ns3:_="">
     <xsd:import namespace="21441324-80bd-4496-af88-aea3a97193ac"/>
@@ -30495,26 +30475,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{372BDECA-AF7C-40CE-A36F-22F75AF5AB95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="21441324-80bd-4496-af88-aea3a97193ac"/>
-    <ds:schemaRef ds:uri="c886050a-9ad4-40b4-a6a1-233234e508b0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="21441324-80bd-4496-af88-aea3a97193ac">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c886050a-9ad4-40b4-a6a1-233234e508b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F45F7F6-1081-4ECB-89E8-010A8DE0840C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E81CEE-6BF5-47C1-AAE8-6ABC6191CF8C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30531,4 +30512,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{372BDECA-AF7C-40CE-A36F-22F75AF5AB95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="21441324-80bd-4496-af88-aea3a97193ac"/>
+    <ds:schemaRef ds:uri="c886050a-9ad4-40b4-a6a1-233234e508b0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F45F7F6-1081-4ECB-89E8-010A8DE0840C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>